--- a/samples/M_应交税费明细表.xlsx
+++ b/samples/M_应交税费明细表.xlsx
@@ -66,12 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,16 +438,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,12 +464,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>本期应交</t>
+          <t>本期计提</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>本期已交</t>
+          <t>本期缴纳</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -477,10 +479,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>税率</t>
+          <t>申报期间</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>是否申报</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -493,23 +500,32 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>150000</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>1820000</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>170000</v>
+        <v>350000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>950000</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>13%</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+          <t>2024年Q4</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>销项税额5,800,000-进项税额600,000=5,200,000</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -518,23 +534,32 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>120000</v>
+        <v>200000</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>300000</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+          <t>2024年Q4</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>利润总额1,200万*25%=300万，预缴250万</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -543,23 +568,32 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>180000</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>180000</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>15000</v>
+        <v>50000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>406000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>364000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>92000</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+          <t>2024年Q4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>增值税5,200,000*7%=364,000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -568,23 +602,100 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>120000</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>120000</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>15000</v>
+        <v>30000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>243600</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>218400</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>55200</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3%+2%</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+          <t>2024年Q4</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>增值税5,200,000*3%=156,000，注意!本期计提243,600有误，应为156,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>地方教育附加</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>162400</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>145600</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>36800</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2024年Q4</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>增值税5,200,000*2%=104,000，注意!本期计提162,400有误，应为104,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>印花税</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2024年Q4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>未申报!需补提购销合同印花税</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
